--- a/Outputs/Scenarios/PtX_demand_SI_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SI_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.000955407017199607</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001142290583912883</v>
+        <v>0.0006187407329528118</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0003807635279709612</v>
+        <v>0.0008995538348313957</v>
       </c>
     </row>
     <row r="18">
@@ -1333,7 +1333,7 @@
         <v>7.656649653298931e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0007903882522875483</v>
+        <v>0.0007903882522875485</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0004634571645962034</v>
       </c>
       <c r="K25" t="n">
-        <v>0.007741930456166546</v>
+        <v>0.007741930456166547</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.376579788500048e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0003807635279709612</v>
+        <v>0.0003855230720705982</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001414363771599922</v>
       </c>
       <c r="K30" t="n">
-        <v>0.006165636098558868</v>
+        <v>0.003339719553386054</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002055212032852956</v>
+        <v>0.004855438427615109</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>7.444019850525905e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002055212032852956</v>
+        <v>0.002080902183263619</v>
       </c>
     </row>
     <row r="43">
